--- a/Shared/Templates/MachineInterfaces/TEMPLATE_INTERFACES_v0.0.xlsx
+++ b/Shared/Templates/MachineInterfaces/TEMPLATE_INTERFACES_v0.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bogdan.dragoi\Desktop\Safety Validation Template\Interface Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Shared\Templates\MachineInterfaces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5E4437-1F63-40BD-B80E-5F5C462553A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786AA4EE-BAE1-40B4-99DB-AB0592A020E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="&lt;GENERIC&gt;" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="55">
   <si>
     <t>Category</t>
   </si>
@@ -78,78 +78,6 @@
     <t>SAFETY_ENCODER</t>
   </si>
   <si>
-    <t>SAFETY_DOORS</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; EMERGENCY READY TO RESET</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; POWER CUT</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; SAFETY ENCODER FAILURE</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; EMERGENCY OK</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; SAFETY DOOR OPEN 1</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; SAFETY DOOR OPEN 2</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; SAFETY DOOR OPEN 3</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; SAFETY DOOR OPEN 4</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; SAFETY DOOR OPEN 5</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; SAFETY DOOR OPEN 6</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; SAFETY DOOR OPEN 7</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; SAFETY DOOR OPEN 8</t>
-  </si>
-  <si>
-    <t>PNC_Q_Sorter&lt;index&gt; HEARTBEAT</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; SORTER RUNNING</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; EMERGENCY RESET</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; OPEN DOOR REQUEST 1</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; OPEN DOOR REQUEST 2</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; OPEN DOOR REQUEST 3</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; OPEN DOOR REQUEST 4</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; OPEN DOOR REQUEST 5</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; OPEN DOOR REQUEST 6</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; OPEN DOOR REQUEST 7</t>
-  </si>
-  <si>
-    <t>PNC_I_Sorter&lt;index&gt; OPEN DOOR REQUEST 8</t>
-  </si>
-  <si>
     <t>SORTER_STATE</t>
   </si>
   <si>
@@ -199,13 +127,88 @@
   </si>
   <si>
     <t>01</t>
+  </si>
+  <si>
+    <t>Signal Name Side 3</t>
+  </si>
+  <si>
+    <t>Expression Side 1</t>
+  </si>
+  <si>
+    <t>"Clock 1Hz"</t>
+  </si>
+  <si>
+    <t>AREA</t>
+  </si>
+  <si>
+    <t>DOORS</t>
+  </si>
+  <si>
+    <t>BREAKERS</t>
+  </si>
+  <si>
+    <t>ENCODER</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>diag_cabinet</t>
+  </si>
+  <si>
+    <t>swp_cabinet</t>
+  </si>
+  <si>
+    <t>diag_bit</t>
+  </si>
+  <si>
+    <t>Blinking 1Hz</t>
+  </si>
+  <si>
+    <t>Awaiting EMERGENCY RESET for the area</t>
+  </si>
+  <si>
+    <t>Sorter Running Soft-Feedback</t>
+  </si>
+  <si>
+    <t>Commissioning-Only EMERGENCY_RESET command</t>
+  </si>
+  <si>
+    <t>PNC_Q_SORTER-&lt;index&gt; HEARTBEAT</t>
+  </si>
+  <si>
+    <t>PNC_Q_SORTER-&lt;index&gt; POWER ENABLED - NOT CUT</t>
+  </si>
+  <si>
+    <t>PNC_Q_SORTER-&lt;index&gt; EMERGENCY READY TO RESET</t>
+  </si>
+  <si>
+    <t>PNC_Q_SORTER-&lt;index&gt; EMERGENCY OK</t>
+  </si>
+  <si>
+    <t>PNC_Q_SORTER-&lt;index&gt; SAFETY ENCODER FAILURE</t>
+  </si>
+  <si>
+    <t>PNC_I_SORTER-&lt;index&gt; SORTER- RUNNING</t>
+  </si>
+  <si>
+    <t>PNC_I_SORTER-&lt;index&gt; EMERGENCY RESET</t>
+  </si>
+  <si>
+    <t>Safety Circuit Energized  by PLC (READY)</t>
+  </si>
+  <si>
+    <t>EMERGENCY Circuit Energized by PLC (READY)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +252,19 @@
       <name val="BankGothic Md BT"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -270,7 +286,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -278,11 +294,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -307,11 +334,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -387,135 +438,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Consolas"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -650,6 +572,181 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Consolas"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -742,7 +839,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2E77BB33-6EF5-41F1-97DF-E1B2FDE000E9}" name="Table136" displayName="Table136" ref="A1:M44" totalsRowShown="0" headerRowDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2E77BB33-6EF5-41F1-97DF-E1B2FDE000E9}" name="Table136" displayName="Table136" ref="A1:M44" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="A1:M44" xr:uid="{BD5F56E4-42F7-4B47-A01A-6A36C5799C78}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{C1A8CDCC-A977-4886-BD75-AE518474E3DF}" name="Category"/>
@@ -752,9 +849,9 @@
     <tableColumn id="5" xr3:uid="{1B858B7E-BA05-4C61-B5D4-0AA69D52F51C}" name="Device"/>
     <tableColumn id="6" xr3:uid="{190E8FA4-A5FF-4849-97AA-41F5BCAA1766}" name="Data Type"/>
     <tableColumn id="13" xr3:uid="{268EC156-9C71-463F-98E4-3C1B5A8CC9BF}" name="Direction &lt;/&gt;"/>
-    <tableColumn id="11" xr3:uid="{00C51FB6-596D-4F73-BDB0-A3C40B7DA874}" name="I/O Offset Byte" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{F936A1C3-04B9-4F63-BBC0-D4C67406CF83}" name="I/O Bit" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{F926F189-4B16-4E3C-A067-9C08DCD9F7B9}" name="I/O Address Side 1" dataDxfId="22">
+    <tableColumn id="11" xr3:uid="{00C51FB6-596D-4F73-BDB0-A3C40B7DA874}" name="I/O Offset Byte" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{F936A1C3-04B9-4F63-BBC0-D4C67406CF83}" name="I/O Bit" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{F926F189-4B16-4E3C-A067-9C08DCD9F7B9}" name="I/O Address Side 1" dataDxfId="10">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.iSynt, $AE$2,
     _xlpm.qSynt, $AF$2,
@@ -774,7 +871,7 @@
     )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{73FDEC40-5CAB-4B64-BA28-16B9F9537BC7}" name="I/O Address Side 2" dataDxfId="21">
+    <tableColumn id="8" xr3:uid="{73FDEC40-5CAB-4B64-BA28-16B9F9537BC7}" name="I/O Address Side 2" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.iSynt, $AE$3,
     _xlpm.qSynt, $AF$3,
@@ -802,15 +899,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0344D3CD-2009-4D05-9865-F62CDA949DFB}" name="Table42" displayName="Table42" ref="AB1:AG3" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0344D3CD-2009-4D05-9865-F62CDA949DFB}" name="Table42" displayName="Table42" ref="AB1:AG3" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="AB1:AG3" xr:uid="{0344D3CD-2009-4D05-9865-F62CDA949DFB}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{107172B9-7F4A-4F64-8D8B-CCBCBA078E6A}" name="Side" totalsRowLabel="Total" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{812BC246-EB7A-4D1D-8F07-82370622A660}" name="Index" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{A374297D-8F14-48CC-B1A8-627D8EDA20AB}" name="Base Node" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{9AB263BD-7BD3-4F20-B2D8-7B2C51D1008D}" name="Base Address" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{DE6D9FCA-863D-42BF-8D1F-FA1F81EBF618}" name="Input Format" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{72E1BF84-3370-434F-BE6D-E8E3C8339F1D}" name="Output Format" totalsRowFunction="count" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{107172B9-7F4A-4F64-8D8B-CCBCBA078E6A}" name="Side" totalsRowLabel="Total" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{812BC246-EB7A-4D1D-8F07-82370622A660}" name="Index" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{A374297D-8F14-48CC-B1A8-627D8EDA20AB}" name="Base Node" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{9AB263BD-7BD3-4F20-B2D8-7B2C51D1008D}" name="Base Address" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{DE6D9FCA-863D-42BF-8D1F-FA1F81EBF618}" name="Input Format" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{72E1BF84-3370-434F-BE6D-E8E3C8339F1D}" name="Output Format" totalsRowFunction="count" dataDxfId="1">
       <calculatedColumnFormula>SUBSTITUTE(Table42[[#This Row],[Input Format]], "I", "Q")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -819,79 +916,98 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5B16194E-0729-47A9-8175-110B6465E684}" name="Table13" displayName="Table13" ref="A1:M31" totalsRowShown="0" headerRowDxfId="20">
-  <autoFilter ref="A1:M31" xr:uid="{BD5F56E4-42F7-4B47-A01A-6A36C5799C78}"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5B16194E-0729-47A9-8175-110B6465E684}" name="SORTER_SIGNALS" displayName="SORTER_SIGNALS" ref="A1:Q31" totalsRowShown="0" headerRowDxfId="33">
+  <autoFilter ref="A1:Q31" xr:uid="{BD5F56E4-42F7-4B47-A01A-6A36C5799C78}"/>
+  <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{70AFEB14-C5E1-45B5-ACF7-FEA119CEAE3F}" name="Category"/>
     <tableColumn id="2" xr3:uid="{31CD88D7-D404-4FD1-B0A7-63DC92F748EB}" name="Description"/>
     <tableColumn id="3" xr3:uid="{CD17E971-CBFB-4819-984B-15E95230E7BA}" name="Functional Unit"/>
     <tableColumn id="4" xr3:uid="{26C9254A-88AA-424F-A480-78A5E7C2E038}" name="Location"/>
     <tableColumn id="5" xr3:uid="{1A4844D7-C1BA-4986-A65A-D47F84E7F24D}" name="Device"/>
+    <tableColumn id="17" xr3:uid="{E2BA662C-1CD5-4D7D-A1BD-FFF5ACA0E9B9}" name="diag_cabinet"/>
+    <tableColumn id="16" xr3:uid="{2322B289-9E4D-4C8C-B770-590A4F1138ED}" name="swp_cabinet"/>
+    <tableColumn id="15" xr3:uid="{2AAA4789-08FA-4501-A2BA-1B0EE64B2B6D}" name="diag_bit"/>
     <tableColumn id="6" xr3:uid="{07406B08-87F7-430C-8CAC-28374B7E47F7}" name="Data Type"/>
     <tableColumn id="13" xr3:uid="{839D26DF-B1E4-434D-8ACC-2388AF9A234B}" name="Direction &lt;/&gt;"/>
-    <tableColumn id="11" xr3:uid="{D9A92227-F013-4F6C-A588-9E9574C4CE1C}" name="I/O Offset Byte" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{97652BB8-44DD-42EE-A425-E9378B3874F2}" name="I/O Bit" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{20279FC3-8E91-4148-95EF-4F832327013B}" name="I/O Address Side 1" dataDxfId="17">
+    <tableColumn id="11" xr3:uid="{D9A92227-F013-4F6C-A588-9E9574C4CE1C}" name="I/O Offset Byte" dataDxfId="32"/>
+    <tableColumn id="12" xr3:uid="{97652BB8-44DD-42EE-A425-E9378B3874F2}" name="I/O Bit" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{20279FC3-8E91-4148-95EF-4F832327013B}" name="I/O Address Side 1" dataDxfId="30">
       <calculatedColumnFormula>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B3774950-E106-4DC0-85A9-5D41FBC53BDD}" name="I/O Address Side 2" dataDxfId="16">
+    <tableColumn id="8" xr3:uid="{B3774950-E106-4DC0-85A9-5D41FBC53BDD}" name="I/O Address Side 2" dataDxfId="29">
       <calculatedColumnFormula>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
 )</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{E277C042-06B1-488A-8023-98334BC8CA03}" name="Signal Name Side 1"/>
-    <tableColumn id="10" xr3:uid="{63179C02-3117-44E0-8ADF-E43A33471E53}" name="Signal Name Side 2"/>
+    <tableColumn id="10" xr3:uid="{63179C02-3117-44E0-8ADF-E43A33471E53}" name="Expression Side 1"/>
+    <tableColumn id="14" xr3:uid="{E894E139-42A3-47CD-8AEC-CDF0EF3B26FE}" name="Signal Name Side 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2DEF310B-D2FF-409B-800B-32DEE4D09497}" name="Table4" displayName="Table4" ref="AB1:AG3" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="AB1:AG3" xr:uid="{2DEF310B-D2FF-409B-800B-32DEE4D09497}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2DEF310B-D2FF-409B-800B-32DEE4D09497}" name="SORTER_PARAMS" displayName="SORTER_PARAMS" ref="AE1:AJ3" headerRowDxfId="28" dataDxfId="27">
+  <autoFilter ref="AE1:AJ3" xr:uid="{2DEF310B-D2FF-409B-800B-32DEE4D09497}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{073AB027-DF21-429E-926A-E480A7A031D1}" name="Side" totalsRowLabel="Total" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{33585E7D-84FF-42F5-8EAB-E70E60C79C49}" name="Index" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{E9A844EA-1484-4738-9D81-B2D93ECAEF6F}" name="Base Node" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{0BA6C34E-489A-43C6-91C7-062D0DAC2C94}" name="Base Address" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{E9B04ED3-08FF-4717-9482-3B28E745B6E4}" name="Input Format" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{4FAECBD4-19AA-49D2-8A36-6C2BE366A78C}" name="Output Format" totalsRowFunction="count" dataDxfId="11">
-      <calculatedColumnFormula>SUBSTITUTE(Table4[[#This Row],[Input Format]], "I", "Q")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{073AB027-DF21-429E-926A-E480A7A031D1}" name="Side" totalsRowLabel="Total" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{33585E7D-84FF-42F5-8EAB-E70E60C79C49}" name="Index" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{E9A844EA-1484-4738-9D81-B2D93ECAEF6F}" name="Base Node" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{0BA6C34E-489A-43C6-91C7-062D0DAC2C94}" name="Base Address" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{E9B04ED3-08FF-4717-9482-3B28E745B6E4}" name="Input Format" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{4FAECBD4-19AA-49D2-8A36-6C2BE366A78C}" name="Output Format" totalsRowFunction="count" dataDxfId="0">
+      <calculatedColumnFormula>SUBSTITUTE(SORTER_PARAMS[[#This Row],[Input Format]], "I", "Q")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{49A0F27A-5277-4288-B892-00BA3E02835B}" name="SORTER_EXTRA_DATA" displayName="SORTER_EXTRA_DATA" ref="AE5:AJ6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="AE5:AJ6" xr:uid="{49A0F27A-5277-4288-B892-00BA3E02835B}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{9F6FA0BB-5313-45AE-BF79-7C2A89F0BC13}" name="AREA" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{20505551-3E63-4E83-98EC-23E87B5A5366}" name="DOORS" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{8FCE7592-ABD7-4D6D-ADF2-5F6E6A2890C8}" name="BREAKERS" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{B8E1CD87-1E6B-42F0-9A53-8FC3654B50AD}" name="ENCODER" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{62E2E8FD-B53C-493B-9B64-E4A3EDF20193}" name="Column1" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{C231E184-6AEF-4E1B-B4CB-F8FB545E2992}" name="Column2" dataDxfId="14"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1233,13 +1349,13 @@
         <v>1</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>2</v>
@@ -1254,30 +1370,30 @@
         <v>5</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F2" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8">
@@ -1329,7 +1445,7 @@
         <v>1</v>
       </c>
       <c r="AC2" s="9" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="AD2" s="5">
         <v>10</v>
@@ -1338,7 +1454,7 @@
         <v>10000</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="AG2" s="5" t="str">
         <f>SUBSTITUTE(Table42[[#This Row],[Input Format]], "I", "Q")</f>
@@ -1347,10 +1463,10 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8">
@@ -1403,7 +1519,7 @@
         <v>2</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="AD3" s="5">
         <v>10</v>
@@ -1422,10 +1538,10 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8">
@@ -1477,10 +1593,10 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8">
@@ -1532,10 +1648,10 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F6" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8">
@@ -1587,10 +1703,10 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8">
@@ -1642,10 +1758,10 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F8" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8">
@@ -1697,10 +1813,10 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8">
@@ -1752,10 +1868,10 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H10" s="8">
         <v>1</v>
@@ -1808,10 +1924,10 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8">
@@ -1863,10 +1979,10 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8">
@@ -1918,10 +2034,10 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8">
@@ -1973,10 +2089,10 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8">
@@ -2028,10 +2144,10 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8">
@@ -2083,10 +2199,10 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8">
@@ -2138,10 +2254,10 @@
     </row>
     <row r="17" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8">
@@ -2193,10 +2309,10 @@
     </row>
     <row r="18" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H18" s="8">
         <v>4</v>
@@ -2247,10 +2363,10 @@
     </row>
     <row r="19" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H19" s="8">
         <v>6</v>
@@ -2348,10 +2464,10 @@
     </row>
     <row r="21" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F21" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8">
@@ -2402,10 +2518,10 @@
     </row>
     <row r="22" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8">
@@ -2457,10 +2573,10 @@
     </row>
     <row r="23" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F23" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8">
@@ -2512,10 +2628,10 @@
     </row>
     <row r="24" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F24" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8">
@@ -2567,10 +2683,10 @@
     </row>
     <row r="25" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8">
@@ -2622,10 +2738,10 @@
     </row>
     <row r="26" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F26" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H26" s="8"/>
       <c r="I26" s="8">
@@ -2677,10 +2793,10 @@
     </row>
     <row r="27" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8">
@@ -2732,10 +2848,10 @@
     </row>
     <row r="28" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8">
@@ -2787,10 +2903,10 @@
     </row>
     <row r="29" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H29" s="8">
         <v>1</v>
@@ -2843,10 +2959,10 @@
     </row>
     <row r="30" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8">
@@ -2898,10 +3014,10 @@
     </row>
     <row r="31" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F31" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="8">
@@ -2953,10 +3069,10 @@
     </row>
     <row r="32" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F32" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="8">
@@ -3008,10 +3124,10 @@
     </row>
     <row r="33" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="8">
@@ -3063,10 +3179,10 @@
     </row>
     <row r="34" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="8">
@@ -3118,10 +3234,10 @@
     </row>
     <row r="35" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F35" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="8">
@@ -3173,10 +3289,10 @@
     </row>
     <row r="36" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="8">
@@ -3228,10 +3344,10 @@
     </row>
     <row r="37" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F37" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H37" s="7">
         <v>4</v>
@@ -3282,10 +3398,10 @@
     </row>
     <row r="38" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H38" s="7">
         <v>6</v>
@@ -3624,994 +3740,709 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4505C2-AC71-43CC-94FB-0554D3241B01}">
-  <dimension ref="A1:AG31"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.5703125" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" customWidth="1"/>
-    <col min="12" max="12" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.7109375" customWidth="1"/>
-    <col min="14" max="27" width="2.85546875" customWidth="1"/>
-    <col min="28" max="28" width="6.28515625" customWidth="1"/>
-    <col min="29" max="29" width="5.7109375" customWidth="1"/>
-    <col min="30" max="30" width="9.140625" customWidth="1"/>
-    <col min="31" max="31" width="10" customWidth="1"/>
-    <col min="32" max="32" width="34" customWidth="1"/>
-    <col min="33" max="33" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="6" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="10" width="7.5703125" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" customWidth="1"/>
+    <col min="15" max="15" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.7109375" customWidth="1"/>
+    <col min="17" max="17" width="23.28515625" customWidth="1"/>
+    <col min="18" max="30" width="2.85546875" customWidth="1"/>
+    <col min="31" max="31" width="8.5703125" customWidth="1"/>
+    <col min="32" max="32" width="10.140625" customWidth="1"/>
+    <col min="33" max="33" width="11.28515625" customWidth="1"/>
+    <col min="34" max="34" width="10.28515625" customWidth="1"/>
+    <col min="35" max="35" width="34" customWidth="1"/>
+    <col min="36" max="36" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>43</v>
+      <c r="P1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="6">
         <v>0</v>
       </c>
-      <c r="I2" s="6">
+      <c r="L2" s="6">
         <v>0</v>
       </c>
-      <c r="J2" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
+      <c r="M2" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
 )</f>
         <v>Q10000.0</v>
       </c>
-      <c r="K2" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.100.0</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="N2" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>I.10.0.0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG2" s="5">
+        <v>10</v>
+      </c>
+      <c r="AH2" s="5">
+        <v>10000</v>
+      </c>
+      <c r="AI2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB2" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD2" s="5">
-        <v>10</v>
-      </c>
-      <c r="AE2" s="5">
-        <v>10000</v>
-      </c>
-      <c r="AF2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG2" s="5" t="str">
-        <f>SUBSTITUTE(Table4[[#This Row],[Input Format]], "I", "Q")</f>
+      <c r="AJ2" s="5" t="str">
+        <f>SUBSTITUTE(SORTER_PARAMS[[#This Row],[Input Format]], "I", "Q")</f>
         <v>Q&lt;base+offset&gt;/.&lt;bit&gt;</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="6">
         <v>1</v>
       </c>
-      <c r="I3" s="6">
+      <c r="L3" s="6">
         <v>0</v>
       </c>
-      <c r="J3" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
+      <c r="M3" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
 )</f>
         <v>Q10001.0</v>
       </c>
-      <c r="K3" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.101.0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB3" s="5">
+      <c r="N3" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>I.10.1.0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE3" s="5">
         <v>2</v>
       </c>
-      <c r="AC3" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD3" s="5">
+      <c r="AF3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG3" s="5">
         <v>10</v>
       </c>
-      <c r="AE3" s="5">
+      <c r="AH3" s="5">
         <v>0</v>
       </c>
-      <c r="AF3" s="5" t="str">
-        <f>"I." &amp;Table4[[#This Row],[Base Node]] &amp;"&lt;base+offset&gt;/.&lt;bit&gt;"</f>
-        <v>I.10&lt;base+offset&gt;/.&lt;bit&gt;</v>
-      </c>
-      <c r="AG3" s="5" t="str">
-        <f>SUBSTITUTE(Table4[[#This Row],[Input Format]], "I", "Q")</f>
-        <v>Q.10&lt;base+offset&gt;/.&lt;bit&gt;</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AI3" s="5" t="str">
+        <f>"I." &amp;SORTER_PARAMS[[#This Row],[Base Node]] &amp;".&lt;base+offset&gt;/.&lt;bit&gt;"</f>
+        <v>I.10.&lt;base+offset&gt;/.&lt;bit&gt;</v>
+      </c>
+      <c r="AJ3" s="5" t="str">
+        <f>SUBSTITUTE(SORTER_PARAMS[[#This Row],[Input Format]], "I", "O")</f>
+        <v>O.10.&lt;base+offset&gt;/.&lt;bit&gt;</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="8">
+        <f t="shared" ref="K4:K6" si="0">K3</f>
+        <v>1</v>
+      </c>
+      <c r="L4" s="8">
+        <f>L3+1</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>Q10001.1</v>
+      </c>
+      <c r="N4" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>I.10.1.1</v>
+      </c>
+      <c r="O4" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="8">
-        <f t="shared" ref="H4:H14" si="0">H3</f>
-        <v>1</v>
-      </c>
-      <c r="I4" s="8">
-        <f>I3+1</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q10001.1</v>
-      </c>
-      <c r="K4" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.101.1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:36" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="8">
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I5" s="8">
-        <f t="shared" ref="I5:I6" si="1">I4+1</f>
+      <c r="L5" s="8">
+        <f t="shared" ref="L5:L6" si="1">L4+1</f>
         <v>2</v>
       </c>
-      <c r="J5" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
+      <c r="M5" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
 )</f>
         <v>Q10001.2</v>
       </c>
-      <c r="K5" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.101.2</v>
-      </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="N5" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>I.10.1.2</v>
+      </c>
+      <c r="O5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I6" s="8">
+      <c r="L6" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J6" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
+      <c r="M6" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
 )</f>
         <v>Q10001.3</v>
       </c>
-      <c r="K6" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.101.3</v>
-      </c>
-      <c r="L6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="6">
-        <v>2</v>
-      </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q10002.0</v>
-      </c>
-      <c r="K7" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.102.0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="N6" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>I.10.1.3</v>
+      </c>
+      <c r="O6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE6" s="11"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="1"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="J7" s="1"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="I8" s="8">
-        <f>I7+1</f>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>I10000.0</v>
+      </c>
+      <c r="N8" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>O.10.0.0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="8">
         <v>1</v>
       </c>
-      <c r="J8" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q10002.1</v>
-      </c>
-      <c r="K8" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.102.1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="I9" s="8">
-        <f t="shared" ref="I9:I14" si="2">I8+1</f>
-        <v>2</v>
-      </c>
-      <c r="J9" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q10002.2</v>
-      </c>
-      <c r="K9" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.102.2</v>
-      </c>
-      <c r="L9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="I10" s="8">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="J10" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q10002.3</v>
-      </c>
-      <c r="K10" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.102.3</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="I11" s="8">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="J11" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q10002.4</v>
-      </c>
-      <c r="K11" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.102.4</v>
-      </c>
-      <c r="L11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="I12" s="8">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="J12" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q10002.5</v>
-      </c>
-      <c r="K12" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.102.5</v>
-      </c>
-      <c r="L12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="I13" s="8">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="J13" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q10002.6</v>
-      </c>
-      <c r="K13" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.102.6</v>
-      </c>
-      <c r="L13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="8">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="I14" s="8">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="J14" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q10002.7</v>
-      </c>
-      <c r="K14" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I.102.7</v>
-      </c>
-      <c r="L14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G15" s="1"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>I10001.0</v>
+      </c>
+      <c r="N9" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
+        ),
+        ""
+    )
+)</f>
+        <v>O.10.1.0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="J10" s="1"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="J11" s="1"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="J12" s="1"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="J13" s="1"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="J14" s="1"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="J15" s="1"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
 )</f>
         <v/>
       </c>
-      <c r="K15" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
+      <c r="N15" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
@@ -4619,914 +4450,150 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" s="6">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0</v>
-      </c>
-      <c r="J16" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10000.0</v>
-      </c>
-      <c r="K16" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.100.0</v>
-      </c>
-      <c r="L16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1</v>
-      </c>
-      <c r="I17" s="6">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10001.0</v>
-      </c>
-      <c r="K17" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.101.0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="6">
-        <v>2</v>
-      </c>
-      <c r="I18" s="6">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10002.0</v>
-      </c>
-      <c r="K18" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.102.0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" ref="H19:H25" si="3">H18</f>
-        <v>2</v>
-      </c>
-      <c r="I19" s="8">
-        <f>I18+1</f>
-        <v>1</v>
-      </c>
-      <c r="J19" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10002.1</v>
-      </c>
-      <c r="K19" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.102.1</v>
-      </c>
-      <c r="L19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H20" s="8">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I20" s="8">
-        <f t="shared" ref="I20:I25" si="4">I19+1</f>
-        <v>2</v>
-      </c>
-      <c r="J20" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10002.2</v>
-      </c>
-      <c r="K20" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.102.2</v>
-      </c>
-      <c r="L20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I21" s="8">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="J21" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10002.3</v>
-      </c>
-      <c r="K21" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.102.3</v>
-      </c>
-      <c r="L21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" s="8">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I22" s="8">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="J22" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10002.4</v>
-      </c>
-      <c r="K22" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.102.4</v>
-      </c>
-      <c r="L22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H23" s="8">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I23" s="8">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="J23" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10002.5</v>
-      </c>
-      <c r="K23" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.102.5</v>
-      </c>
-      <c r="L23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H24" s="8">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I24" s="8">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="J24" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10002.6</v>
-      </c>
-      <c r="K24" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.102.6</v>
-      </c>
-      <c r="L24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="8">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I25" s="8">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="J25" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>I10002.7</v>
-      </c>
-      <c r="K25" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v>Q.102.7</v>
-      </c>
-      <c r="L25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G26" s="1"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="J16" s="1"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+    </row>
+    <row r="17" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J17" s="1"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+    </row>
+    <row r="18" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J18" s="1"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+    </row>
+    <row r="19" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J19" s="1"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+    </row>
+    <row r="20" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J20" s="1"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+    </row>
+    <row r="21" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J21" s="1"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+    </row>
+    <row r="22" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J22" s="1"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+    </row>
+    <row r="23" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J23" s="1"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J24" s="1"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+    </row>
+    <row r="25" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J25" s="1"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+    </row>
+    <row r="26" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J26" s="1"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+    </row>
+    <row r="27" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J27" s="1"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+    </row>
+    <row r="28" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J28" s="1"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+    </row>
+    <row r="29" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J29" s="1"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+    </row>
+    <row r="30" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="J30" s="1"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+    </row>
+    <row r="31" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$2,
+    _xlpm.qSynt, $AJ$2,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$2 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
 )</f>
         <v/>
       </c>
-      <c r="K26" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G27" s="1"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-      <c r="K27" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G28" s="1"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-      <c r="K28" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G29" s="1"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-      <c r="K29" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G30" s="1"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-      <c r="K30" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$2,
-    _xlpm.qSynt, $AG$2,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$2 + Table13[[#This Row],[I/O Offset Byte]]
-        ),
-        ""
-    )
-)</f>
-        <v/>
-      </c>
-      <c r="K31" s="7" t="str">
-        <f>_xlfn.LET(
-    _xlpm.iSynt, $AF$3,
-    _xlpm.qSynt, $AG$3,
-    _xlpm.synt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(Table13[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
-    IF(
-        _xlpm.synt &lt;&gt; "",
-        SUBSTITUTE(
-            IF(
-                Table13[[#This Row],[Data Type]] = "BOOL",
-                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", Table13[[#This Row],[I/O Bit]]),
-                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
-            ),
-            "&lt;base+offset&gt;",
-            $AE$3 + Table13[[#This Row],[I/O Offset Byte]]
+      <c r="N31" s="7" t="str">
+        <f>_xlfn.LET(
+    _xlpm.iSynt, $AI$3,
+    _xlpm.qSynt, $AJ$3,
+    _xlpm.synt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&gt;", _xlpm.iSynt, IF(SORTER_SIGNALS[[#This Row],[Direction &lt;/&gt;]] = "&lt;", _xlpm.qSynt, "")),
+    IF(
+        _xlpm.synt &lt;&gt; "",
+        SUBSTITUTE(
+            IF(
+                SORTER_SIGNALS[[#This Row],[Data Type]] = "BOOL",
+                SUBSTITUTE(SUBSTITUTE(_xlpm.synt, "/", ""), "&lt;bit&gt;", SORTER_SIGNALS[[#This Row],[I/O Bit]]),
+                _xlfn.TEXTBEFORE(_xlpm.synt, "/")
+            ),
+            "&lt;base+offset&gt;",
+            $AH$3 + SORTER_SIGNALS[[#This Row],[I/O Offset Byte]]
         ),
         ""
     )
@@ -5540,9 +4607,10 @@
   <headerFooter>
     <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Public&amp;1#_x000D_</oddHeader>
   </headerFooter>
-  <tableParts count="2">
+  <tableParts count="3">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
